--- a/analysis/data/raw_data/06_timelinedata.xlsx
+++ b/analysis/data/raw_data/06_timelinedata.xlsx
@@ -1,35 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pedersen\PotteryChronology_IND\analysis\data\raw_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soere\Documents\PotteryChronology_IND\analysis\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AADC26-5FA1-4C7D-9852-C2C84BC106B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C120D571-1EAF-4D83-8E22-C2214FF2A36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9656298-5508-4E8D-B9E7-EAD329E3AC19}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E9656298-5508-4E8D-B9E7-EAD329E3AC19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2204,9 +2193,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 Tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2244,7 +2233,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2350,7 +2339,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2492,7 +2481,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -34595,8 +34584,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q612">
-    <sortCondition ref="D1:D612"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q613">
+    <sortCondition ref="D1:D613"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
